--- a/main/ig/StructureDefinition-DocumentReference.xlsx
+++ b/main/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:09:15+00:00</t>
+    <t>2025-03-05T10:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
